--- a/dashboard-report.xlsx
+++ b/dashboard-report.xlsx
@@ -415,7 +415,7 @@
         <v>Período</v>
       </c>
       <c r="B3" t="str">
-        <v>22/4/2026</v>
+        <v>24/4/2026</v>
       </c>
     </row>
     <row r="5">

--- a/dashboard-report.xlsx
+++ b/dashboard-report.xlsx
@@ -415,7 +415,7 @@
         <v>Período</v>
       </c>
       <c r="B3" t="str">
-        <v>24/4/2026</v>
+        <v>14/5/2026</v>
       </c>
     </row>
     <row r="5">

--- a/dashboard-report.xlsx
+++ b/dashboard-report.xlsx
@@ -415,7 +415,7 @@
         <v>Período</v>
       </c>
       <c r="B3" t="str">
-        <v>14/5/2026</v>
+        <v>17/5/2026</v>
       </c>
     </row>
     <row r="5">

--- a/dashboard-report.xlsx
+++ b/dashboard-report.xlsx
@@ -415,7 +415,7 @@
         <v>Período</v>
       </c>
       <c r="B3" t="str">
-        <v>17/5/2026</v>
+        <v>26/5/2026</v>
       </c>
     </row>
     <row r="5">

--- a/dashboard-report.xlsx
+++ b/dashboard-report.xlsx
@@ -415,7 +415,7 @@
         <v>Período</v>
       </c>
       <c r="B3" t="str">
-        <v>26/5/2026</v>
+        <v>5/6/2026</v>
       </c>
     </row>
     <row r="5">
